--- a/data_after_engineering/09 Template Deliverable.xlsx
+++ b/data_after_engineering/09 Template Deliverable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\KLTC-UIS\RMPOC\General\Dataworks\Data Works\Cases\Final Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0BAA0A7-42CC-42C9-884F-7C01B13D4F5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38DFB2B0-7B39-4651-9AAD-6CCB1F5E5E77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="9" xr2:uid="{61329E2B-AA4D-40FF-A9E6-EA1F3C5A028D}"/>
+    <workbookView xWindow="-33017" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{61329E2B-AA4D-40FF-A9E6-EA1F3C5A028D}"/>
   </bookViews>
   <sheets>
     <sheet name="Case 1" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="83">
   <si>
     <t>Date</t>
   </si>
@@ -489,11 +489,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
@@ -837,229 +835,669 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2AA265E-1AAD-4A60-928A-E6B523E71404}">
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E81"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.7265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="32.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="5" t="s">
         <v>43</v>
       </c>
       <c r="E1" s="1"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="7"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="6" t="s">
         <v>2</v>
       </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="7"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="6" t="s">
         <v>3</v>
       </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="7"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="6" t="s">
         <v>4</v>
       </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="7"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="6" t="s">
         <v>5</v>
       </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="7"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="6" t="s">
         <v>6</v>
       </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="7"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="6" t="s">
         <v>7</v>
       </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="7"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="6" t="s">
         <v>8</v>
       </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="7"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="7"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="6" t="s">
         <v>10</v>
       </c>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="7"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="6" t="s">
         <v>11</v>
       </c>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="7"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="6" t="s">
         <v>12</v>
       </c>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="7"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="6" t="s">
         <v>13</v>
       </c>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="7"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="6" t="s">
         <v>14</v>
       </c>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="7"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="6" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A17" s="2" t="s">
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="7"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" s="6" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A18" s="2" t="s">
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="7"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A19" s="2" t="s">
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="7"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" s="6" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A20" s="2" t="s">
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="7"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" s="6" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A21" s="2" t="s">
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="7"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" s="6" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A22" s="2" t="s">
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="7"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" s="6" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A23" s="2" t="s">
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="7"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" s="6" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A24" s="2" t="s">
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="7"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" s="6" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A25" s="2" t="s">
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="7"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" s="6" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A26" s="2" t="s">
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="7"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26" s="6" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A27" s="2" t="s">
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="7"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" s="6" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A28" s="2" t="s">
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="7"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" s="6" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A29" s="2" t="s">
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="7"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29" s="6" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A30" s="2" t="s">
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="7"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30" s="6" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A31" s="2" t="s">
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="7"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31" s="6" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A32" s="2" t="s">
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="7"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32" s="6" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A33" s="2" t="s">
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="7"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33" s="6" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A34" s="2" t="s">
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="7"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34" s="6" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A35" s="2" t="s">
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="7"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35" s="6" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A36" s="2" t="s">
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="7"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36" s="6" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A37" s="2" t="s">
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="7"/>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37" s="6" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A38" s="2" t="s">
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="7"/>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38" s="6" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A39" s="2" t="s">
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="7"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39" s="6" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A40" s="2" t="s">
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="7"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A40" s="6" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A41" s="2" t="s">
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="7"/>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A41" s="6" t="s">
         <v>40</v>
       </c>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="7"/>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A42" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="7"/>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A43" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="7"/>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="7"/>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A45" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="7"/>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A46" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="7"/>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A47" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="7"/>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A48" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="7"/>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A49" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="7"/>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A50" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="7"/>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A51" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="7"/>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A52" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="7"/>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A53" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B53" s="2"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="7"/>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A54" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B54" s="2"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="7"/>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A55" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="7"/>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A56" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="7"/>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A57" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="7"/>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A58" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B58" s="2"/>
+      <c r="C58" s="2"/>
+      <c r="D58" s="7"/>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A59" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="7"/>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A60" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B60" s="2"/>
+      <c r="C60" s="2"/>
+      <c r="D60" s="7"/>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A61" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B61" s="2"/>
+      <c r="C61" s="2"/>
+      <c r="D61" s="7"/>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A62" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B62" s="2"/>
+      <c r="C62" s="2"/>
+      <c r="D62" s="7"/>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A63" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B63" s="2"/>
+      <c r="C63" s="2"/>
+      <c r="D63" s="7"/>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A64" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B64" s="2"/>
+      <c r="C64" s="2"/>
+      <c r="D64" s="7"/>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A65" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B65" s="2"/>
+      <c r="C65" s="2"/>
+      <c r="D65" s="7"/>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A66" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B66" s="2"/>
+      <c r="C66" s="2"/>
+      <c r="D66" s="7"/>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A67" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B67" s="2"/>
+      <c r="C67" s="2"/>
+      <c r="D67" s="7"/>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A68" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B68" s="2"/>
+      <c r="C68" s="2"/>
+      <c r="D68" s="7"/>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A69" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B69" s="2"/>
+      <c r="C69" s="2"/>
+      <c r="D69" s="7"/>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A70" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B70" s="2"/>
+      <c r="C70" s="2"/>
+      <c r="D70" s="7"/>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A71" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B71" s="2"/>
+      <c r="C71" s="2"/>
+      <c r="D71" s="7"/>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A72" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B72" s="2"/>
+      <c r="C72" s="2"/>
+      <c r="D72" s="7"/>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A73" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="B73" s="2"/>
+      <c r="C73" s="2"/>
+      <c r="D73" s="7"/>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A74" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B74" s="2"/>
+      <c r="C74" s="2"/>
+      <c r="D74" s="7"/>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A75" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="B75" s="2"/>
+      <c r="C75" s="2"/>
+      <c r="D75" s="7"/>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A76" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="7"/>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A77" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B77" s="2"/>
+      <c r="C77" s="2"/>
+      <c r="D77" s="7"/>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A78" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B78" s="2"/>
+      <c r="C78" s="2"/>
+      <c r="D78" s="7"/>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A79" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B79" s="2"/>
+      <c r="C79" s="2"/>
+      <c r="D79" s="7"/>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A80" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B80" s="2"/>
+      <c r="C80" s="2"/>
+      <c r="D80" s="7"/>
+    </row>
+    <row r="81" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A81" s="8">
+        <v>46753</v>
+      </c>
+      <c r="B81" s="9"/>
+      <c r="C81" s="9"/>
+      <c r="D81" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1078,658 +1516,658 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="5" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="9"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="7"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="9"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="7"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="9"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="7"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="9"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="7"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="9"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="7"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="9"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="7"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="9"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="7"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="9"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="7"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="9"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="7"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="9"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="7"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="9"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="7"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="9"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="7"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="9"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="7"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="9"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="7"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="9"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="7"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="9"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="7"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="9"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="7"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="9"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="7"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="9"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="7"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="9"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="7"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="9"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="7"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="9"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="7"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="9"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="7"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="9"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="7"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" s="8" t="s">
+      <c r="A26" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="9"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="7"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="9"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="7"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="9"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="7"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="9"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="7"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" s="8" t="s">
+      <c r="A30" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="9"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="7"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="9"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="7"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" s="8" t="s">
+      <c r="A32" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="9"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="7"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" s="8" t="s">
+      <c r="A33" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="9"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="7"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" s="8" t="s">
+      <c r="A34" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="9"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="7"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" s="8" t="s">
+      <c r="A35" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="9"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="7"/>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" s="8" t="s">
+      <c r="A36" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="9"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="7"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A37" s="8" t="s">
+      <c r="A37" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="9"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="7"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38" s="8" t="s">
+      <c r="A38" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="9"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="7"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39" s="8" t="s">
+      <c r="A39" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="9"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="7"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A40" s="8" t="s">
+      <c r="A40" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B40" s="4"/>
-      <c r="C40" s="4"/>
-      <c r="D40" s="9"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="7"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" s="8" t="s">
+      <c r="A41" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
-      <c r="D41" s="9"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="7"/>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42" s="8" t="s">
+      <c r="A42" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="9"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="7"/>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A43" s="8" t="s">
+      <c r="A43" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B43" s="4"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="9"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="7"/>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A44" s="8" t="s">
+      <c r="A44" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B44" s="4"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="9"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="7"/>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A45" s="8" t="s">
+      <c r="A45" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B45" s="4"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="9"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="7"/>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A46" s="8" t="s">
+      <c r="A46" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B46" s="4"/>
-      <c r="C46" s="4"/>
-      <c r="D46" s="9"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="7"/>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A47" s="8" t="s">
+      <c r="A47" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B47" s="4"/>
-      <c r="C47" s="4"/>
-      <c r="D47" s="9"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="7"/>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A48" s="8" t="s">
+      <c r="A48" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B48" s="4"/>
-      <c r="C48" s="4"/>
-      <c r="D48" s="9"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="7"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A49" s="8" t="s">
+      <c r="A49" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B49" s="4"/>
-      <c r="C49" s="4"/>
-      <c r="D49" s="9"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="7"/>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A50" s="8" t="s">
+      <c r="A50" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B50" s="4"/>
-      <c r="C50" s="4"/>
-      <c r="D50" s="9"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="7"/>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A51" s="8" t="s">
+      <c r="A51" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B51" s="4"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="9"/>
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="7"/>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A52" s="8" t="s">
+      <c r="A52" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B52" s="4"/>
-      <c r="C52" s="4"/>
-      <c r="D52" s="9"/>
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="7"/>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A53" s="8" t="s">
+      <c r="A53" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B53" s="4"/>
-      <c r="C53" s="4"/>
-      <c r="D53" s="9"/>
+      <c r="B53" s="2"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="7"/>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A54" s="8" t="s">
+      <c r="A54" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B54" s="4"/>
-      <c r="C54" s="4"/>
-      <c r="D54" s="9"/>
+      <c r="B54" s="2"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="7"/>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A55" s="8" t="s">
+      <c r="A55" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B55" s="4"/>
-      <c r="C55" s="4"/>
-      <c r="D55" s="9"/>
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="7"/>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A56" s="8" t="s">
+      <c r="A56" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="B56" s="4"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="9"/>
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="7"/>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A57" s="8" t="s">
+      <c r="A57" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="B57" s="4"/>
-      <c r="C57" s="4"/>
-      <c r="D57" s="9"/>
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="7"/>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A58" s="8" t="s">
+      <c r="A58" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="B58" s="4"/>
-      <c r="C58" s="4"/>
-      <c r="D58" s="9"/>
+      <c r="B58" s="2"/>
+      <c r="C58" s="2"/>
+      <c r="D58" s="7"/>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A59" s="8" t="s">
+      <c r="A59" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B59" s="4"/>
-      <c r="C59" s="4"/>
-      <c r="D59" s="9"/>
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="7"/>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A60" s="8" t="s">
+      <c r="A60" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B60" s="4"/>
-      <c r="C60" s="4"/>
-      <c r="D60" s="9"/>
+      <c r="B60" s="2"/>
+      <c r="C60" s="2"/>
+      <c r="D60" s="7"/>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A61" s="8" t="s">
+      <c r="A61" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="B61" s="4"/>
-      <c r="C61" s="4"/>
-      <c r="D61" s="9"/>
+      <c r="B61" s="2"/>
+      <c r="C61" s="2"/>
+      <c r="D61" s="7"/>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A62" s="8" t="s">
+      <c r="A62" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B62" s="4"/>
-      <c r="C62" s="4"/>
-      <c r="D62" s="9"/>
+      <c r="B62" s="2"/>
+      <c r="C62" s="2"/>
+      <c r="D62" s="7"/>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A63" s="8" t="s">
+      <c r="A63" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B63" s="4"/>
-      <c r="C63" s="4"/>
-      <c r="D63" s="9"/>
+      <c r="B63" s="2"/>
+      <c r="C63" s="2"/>
+      <c r="D63" s="7"/>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A64" s="8" t="s">
+      <c r="A64" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="B64" s="4"/>
-      <c r="C64" s="4"/>
-      <c r="D64" s="9"/>
+      <c r="B64" s="2"/>
+      <c r="C64" s="2"/>
+      <c r="D64" s="7"/>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A65" s="8" t="s">
+      <c r="A65" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B65" s="4"/>
-      <c r="C65" s="4"/>
-      <c r="D65" s="9"/>
+      <c r="B65" s="2"/>
+      <c r="C65" s="2"/>
+      <c r="D65" s="7"/>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A66" s="8" t="s">
+      <c r="A66" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="B66" s="4"/>
-      <c r="C66" s="4"/>
-      <c r="D66" s="9"/>
+      <c r="B66" s="2"/>
+      <c r="C66" s="2"/>
+      <c r="D66" s="7"/>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A67" s="8" t="s">
+      <c r="A67" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B67" s="4"/>
-      <c r="C67" s="4"/>
-      <c r="D67" s="9"/>
+      <c r="B67" s="2"/>
+      <c r="C67" s="2"/>
+      <c r="D67" s="7"/>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A68" s="8" t="s">
+      <c r="A68" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B68" s="4"/>
-      <c r="C68" s="4"/>
-      <c r="D68" s="9"/>
+      <c r="B68" s="2"/>
+      <c r="C68" s="2"/>
+      <c r="D68" s="7"/>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A69" s="8" t="s">
+      <c r="A69" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="B69" s="4"/>
-      <c r="C69" s="4"/>
-      <c r="D69" s="9"/>
+      <c r="B69" s="2"/>
+      <c r="C69" s="2"/>
+      <c r="D69" s="7"/>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A70" s="8" t="s">
+      <c r="A70" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B70" s="4"/>
-      <c r="C70" s="4"/>
-      <c r="D70" s="9"/>
+      <c r="B70" s="2"/>
+      <c r="C70" s="2"/>
+      <c r="D70" s="7"/>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A71" s="8" t="s">
+      <c r="A71" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B71" s="4"/>
-      <c r="C71" s="4"/>
-      <c r="D71" s="9"/>
+      <c r="B71" s="2"/>
+      <c r="C71" s="2"/>
+      <c r="D71" s="7"/>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A72" s="8" t="s">
+      <c r="A72" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="B72" s="4"/>
-      <c r="C72" s="4"/>
-      <c r="D72" s="9"/>
+      <c r="B72" s="2"/>
+      <c r="C72" s="2"/>
+      <c r="D72" s="7"/>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A73" s="8" t="s">
+      <c r="A73" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="B73" s="4"/>
-      <c r="C73" s="4"/>
-      <c r="D73" s="9"/>
+      <c r="B73" s="2"/>
+      <c r="C73" s="2"/>
+      <c r="D73" s="7"/>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A74" s="8" t="s">
+      <c r="A74" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="B74" s="4"/>
-      <c r="C74" s="4"/>
-      <c r="D74" s="9"/>
+      <c r="B74" s="2"/>
+      <c r="C74" s="2"/>
+      <c r="D74" s="7"/>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A75" s="8" t="s">
+      <c r="A75" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="B75" s="4"/>
-      <c r="C75" s="4"/>
-      <c r="D75" s="9"/>
+      <c r="B75" s="2"/>
+      <c r="C75" s="2"/>
+      <c r="D75" s="7"/>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A76" s="8" t="s">
+      <c r="A76" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="B76" s="4"/>
-      <c r="C76" s="4"/>
-      <c r="D76" s="9"/>
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="7"/>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A77" s="8" t="s">
+      <c r="A77" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="B77" s="4"/>
-      <c r="C77" s="4"/>
-      <c r="D77" s="9"/>
+      <c r="B77" s="2"/>
+      <c r="C77" s="2"/>
+      <c r="D77" s="7"/>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A78" s="8" t="s">
+      <c r="A78" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="B78" s="4"/>
-      <c r="C78" s="4"/>
-      <c r="D78" s="9"/>
+      <c r="B78" s="2"/>
+      <c r="C78" s="2"/>
+      <c r="D78" s="7"/>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A79" s="8" t="s">
+      <c r="A79" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="B79" s="4"/>
-      <c r="C79" s="4"/>
-      <c r="D79" s="9"/>
+      <c r="B79" s="2"/>
+      <c r="C79" s="2"/>
+      <c r="D79" s="7"/>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A80" s="8" t="s">
+      <c r="A80" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="B80" s="4"/>
-      <c r="C80" s="4"/>
-      <c r="D80" s="9"/>
+      <c r="B80" s="2"/>
+      <c r="C80" s="2"/>
+      <c r="D80" s="7"/>
     </row>
     <row r="81" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A81" s="10">
+      <c r="A81" s="8">
         <v>46753</v>
       </c>
-      <c r="B81" s="11"/>
-      <c r="C81" s="11"/>
-      <c r="D81" s="12"/>
+      <c r="B81" s="9"/>
+      <c r="C81" s="9"/>
+      <c r="D81" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -1749,659 +2187,659 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="5" t="s">
         <v>43</v>
       </c>
       <c r="E1" s="1"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="9"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="7"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="9"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="7"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="9"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="7"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="9"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="7"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="9"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="7"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="9"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="7"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="9"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="7"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="9"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="7"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="9"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="7"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="9"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="7"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="9"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="7"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="9"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="7"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="9"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="7"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="9"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="7"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="9"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="7"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="9"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="7"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="9"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="7"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="9"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="7"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="9"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="7"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="9"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="7"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="9"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="7"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="9"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="7"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="9"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="7"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="9"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="7"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" s="8" t="s">
+      <c r="A26" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="9"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="7"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="9"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="7"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="9"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="7"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="9"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="7"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" s="8" t="s">
+      <c r="A30" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="9"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="7"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="9"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="7"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" s="8" t="s">
+      <c r="A32" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="9"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="7"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" s="8" t="s">
+      <c r="A33" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="9"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="7"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" s="8" t="s">
+      <c r="A34" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="9"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="7"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" s="8" t="s">
+      <c r="A35" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="9"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="7"/>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" s="8" t="s">
+      <c r="A36" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="9"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="7"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A37" s="8" t="s">
+      <c r="A37" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="9"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="7"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38" s="8" t="s">
+      <c r="A38" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="9"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="7"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39" s="8" t="s">
+      <c r="A39" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="9"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="7"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A40" s="8" t="s">
+      <c r="A40" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B40" s="4"/>
-      <c r="C40" s="4"/>
-      <c r="D40" s="9"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="7"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" s="8" t="s">
+      <c r="A41" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
-      <c r="D41" s="9"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="7"/>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42" s="8" t="s">
+      <c r="A42" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="9"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="7"/>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A43" s="8" t="s">
+      <c r="A43" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B43" s="4"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="9"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="7"/>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A44" s="8" t="s">
+      <c r="A44" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B44" s="4"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="9"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="7"/>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A45" s="8" t="s">
+      <c r="A45" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B45" s="4"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="9"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="7"/>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A46" s="8" t="s">
+      <c r="A46" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B46" s="4"/>
-      <c r="C46" s="4"/>
-      <c r="D46" s="9"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="7"/>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A47" s="8" t="s">
+      <c r="A47" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B47" s="4"/>
-      <c r="C47" s="4"/>
-      <c r="D47" s="9"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="7"/>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A48" s="8" t="s">
+      <c r="A48" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B48" s="4"/>
-      <c r="C48" s="4"/>
-      <c r="D48" s="9"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="7"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A49" s="8" t="s">
+      <c r="A49" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B49" s="4"/>
-      <c r="C49" s="4"/>
-      <c r="D49" s="9"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="7"/>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A50" s="8" t="s">
+      <c r="A50" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B50" s="4"/>
-      <c r="C50" s="4"/>
-      <c r="D50" s="9"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="7"/>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A51" s="8" t="s">
+      <c r="A51" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B51" s="4"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="9"/>
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="7"/>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A52" s="8" t="s">
+      <c r="A52" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B52" s="4"/>
-      <c r="C52" s="4"/>
-      <c r="D52" s="9"/>
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="7"/>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A53" s="8" t="s">
+      <c r="A53" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B53" s="4"/>
-      <c r="C53" s="4"/>
-      <c r="D53" s="9"/>
+      <c r="B53" s="2"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="7"/>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A54" s="8" t="s">
+      <c r="A54" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B54" s="4"/>
-      <c r="C54" s="4"/>
-      <c r="D54" s="9"/>
+      <c r="B54" s="2"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="7"/>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A55" s="8" t="s">
+      <c r="A55" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B55" s="4"/>
-      <c r="C55" s="4"/>
-      <c r="D55" s="9"/>
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="7"/>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A56" s="8" t="s">
+      <c r="A56" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="B56" s="4"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="9"/>
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="7"/>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A57" s="8" t="s">
+      <c r="A57" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="B57" s="4"/>
-      <c r="C57" s="4"/>
-      <c r="D57" s="9"/>
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="7"/>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A58" s="8" t="s">
+      <c r="A58" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="B58" s="4"/>
-      <c r="C58" s="4"/>
-      <c r="D58" s="9"/>
+      <c r="B58" s="2"/>
+      <c r="C58" s="2"/>
+      <c r="D58" s="7"/>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A59" s="8" t="s">
+      <c r="A59" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B59" s="4"/>
-      <c r="C59" s="4"/>
-      <c r="D59" s="9"/>
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="7"/>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A60" s="8" t="s">
+      <c r="A60" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B60" s="4"/>
-      <c r="C60" s="4"/>
-      <c r="D60" s="9"/>
+      <c r="B60" s="2"/>
+      <c r="C60" s="2"/>
+      <c r="D60" s="7"/>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A61" s="8" t="s">
+      <c r="A61" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="B61" s="4"/>
-      <c r="C61" s="4"/>
-      <c r="D61" s="9"/>
+      <c r="B61" s="2"/>
+      <c r="C61" s="2"/>
+      <c r="D61" s="7"/>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A62" s="8" t="s">
+      <c r="A62" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B62" s="4"/>
-      <c r="C62" s="4"/>
-      <c r="D62" s="9"/>
+      <c r="B62" s="2"/>
+      <c r="C62" s="2"/>
+      <c r="D62" s="7"/>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A63" s="8" t="s">
+      <c r="A63" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B63" s="4"/>
-      <c r="C63" s="4"/>
-      <c r="D63" s="9"/>
+      <c r="B63" s="2"/>
+      <c r="C63" s="2"/>
+      <c r="D63" s="7"/>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A64" s="8" t="s">
+      <c r="A64" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="B64" s="4"/>
-      <c r="C64" s="4"/>
-      <c r="D64" s="9"/>
+      <c r="B64" s="2"/>
+      <c r="C64" s="2"/>
+      <c r="D64" s="7"/>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A65" s="8" t="s">
+      <c r="A65" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B65" s="4"/>
-      <c r="C65" s="4"/>
-      <c r="D65" s="9"/>
+      <c r="B65" s="2"/>
+      <c r="C65" s="2"/>
+      <c r="D65" s="7"/>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A66" s="8" t="s">
+      <c r="A66" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="B66" s="4"/>
-      <c r="C66" s="4"/>
-      <c r="D66" s="9"/>
+      <c r="B66" s="2"/>
+      <c r="C66" s="2"/>
+      <c r="D66" s="7"/>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A67" s="8" t="s">
+      <c r="A67" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B67" s="4"/>
-      <c r="C67" s="4"/>
-      <c r="D67" s="9"/>
+      <c r="B67" s="2"/>
+      <c r="C67" s="2"/>
+      <c r="D67" s="7"/>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A68" s="8" t="s">
+      <c r="A68" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B68" s="4"/>
-      <c r="C68" s="4"/>
-      <c r="D68" s="9"/>
+      <c r="B68" s="2"/>
+      <c r="C68" s="2"/>
+      <c r="D68" s="7"/>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A69" s="8" t="s">
+      <c r="A69" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="B69" s="4"/>
-      <c r="C69" s="4"/>
-      <c r="D69" s="9"/>
+      <c r="B69" s="2"/>
+      <c r="C69" s="2"/>
+      <c r="D69" s="7"/>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A70" s="8" t="s">
+      <c r="A70" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B70" s="4"/>
-      <c r="C70" s="4"/>
-      <c r="D70" s="9"/>
+      <c r="B70" s="2"/>
+      <c r="C70" s="2"/>
+      <c r="D70" s="7"/>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A71" s="8" t="s">
+      <c r="A71" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B71" s="4"/>
-      <c r="C71" s="4"/>
-      <c r="D71" s="9"/>
+      <c r="B71" s="2"/>
+      <c r="C71" s="2"/>
+      <c r="D71" s="7"/>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A72" s="8" t="s">
+      <c r="A72" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="B72" s="4"/>
-      <c r="C72" s="4"/>
-      <c r="D72" s="9"/>
+      <c r="B72" s="2"/>
+      <c r="C72" s="2"/>
+      <c r="D72" s="7"/>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A73" s="8" t="s">
+      <c r="A73" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="B73" s="4"/>
-      <c r="C73" s="4"/>
-      <c r="D73" s="9"/>
+      <c r="B73" s="2"/>
+      <c r="C73" s="2"/>
+      <c r="D73" s="7"/>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A74" s="8" t="s">
+      <c r="A74" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="B74" s="4"/>
-      <c r="C74" s="4"/>
-      <c r="D74" s="9"/>
+      <c r="B74" s="2"/>
+      <c r="C74" s="2"/>
+      <c r="D74" s="7"/>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A75" s="8" t="s">
+      <c r="A75" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="B75" s="4"/>
-      <c r="C75" s="4"/>
-      <c r="D75" s="9"/>
+      <c r="B75" s="2"/>
+      <c r="C75" s="2"/>
+      <c r="D75" s="7"/>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A76" s="8" t="s">
+      <c r="A76" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="B76" s="4"/>
-      <c r="C76" s="4"/>
-      <c r="D76" s="9"/>
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="7"/>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A77" s="8" t="s">
+      <c r="A77" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="B77" s="4"/>
-      <c r="C77" s="4"/>
-      <c r="D77" s="9"/>
+      <c r="B77" s="2"/>
+      <c r="C77" s="2"/>
+      <c r="D77" s="7"/>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A78" s="8" t="s">
+      <c r="A78" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="B78" s="4"/>
-      <c r="C78" s="4"/>
-      <c r="D78" s="9"/>
+      <c r="B78" s="2"/>
+      <c r="C78" s="2"/>
+      <c r="D78" s="7"/>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A79" s="8" t="s">
+      <c r="A79" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="B79" s="4"/>
-      <c r="C79" s="4"/>
-      <c r="D79" s="9"/>
+      <c r="B79" s="2"/>
+      <c r="C79" s="2"/>
+      <c r="D79" s="7"/>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A80" s="8" t="s">
+      <c r="A80" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="B80" s="4"/>
-      <c r="C80" s="4"/>
-      <c r="D80" s="9"/>
+      <c r="B80" s="2"/>
+      <c r="C80" s="2"/>
+      <c r="D80" s="7"/>
     </row>
     <row r="81" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A81" s="10">
+      <c r="A81" s="8">
         <v>46753</v>
       </c>
-      <c r="B81" s="11"/>
-      <c r="C81" s="11"/>
-      <c r="D81" s="12"/>
+      <c r="B81" s="9"/>
+      <c r="C81" s="9"/>
+      <c r="D81" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2420,659 +2858,659 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="5" t="s">
         <v>43</v>
       </c>
       <c r="E1" s="1"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="9"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="7"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="9"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="7"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="9"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="7"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="9"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="7"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="9"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="7"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="9"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="7"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="9"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="7"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="9"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="7"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="9"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="7"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="9"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="7"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="9"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="7"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="9"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="7"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="9"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="7"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="9"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="7"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="9"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="7"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="9"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="7"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="9"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="7"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="9"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="7"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="9"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="7"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="9"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="7"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="9"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="7"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="9"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="7"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="9"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="7"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="9"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="7"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" s="8" t="s">
+      <c r="A26" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="9"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="7"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="9"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="7"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="9"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="7"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="9"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="7"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" s="8" t="s">
+      <c r="A30" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="9"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="7"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="9"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="7"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" s="8" t="s">
+      <c r="A32" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="9"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="7"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" s="8" t="s">
+      <c r="A33" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="9"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="7"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" s="8" t="s">
+      <c r="A34" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="9"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="7"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" s="8" t="s">
+      <c r="A35" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="9"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="7"/>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" s="8" t="s">
+      <c r="A36" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="9"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="7"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A37" s="8" t="s">
+      <c r="A37" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="9"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="7"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38" s="8" t="s">
+      <c r="A38" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="9"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="7"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39" s="8" t="s">
+      <c r="A39" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="9"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="7"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A40" s="8" t="s">
+      <c r="A40" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B40" s="4"/>
-      <c r="C40" s="4"/>
-      <c r="D40" s="9"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="7"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" s="8" t="s">
+      <c r="A41" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
-      <c r="D41" s="9"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="7"/>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42" s="8" t="s">
+      <c r="A42" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="9"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="7"/>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A43" s="8" t="s">
+      <c r="A43" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B43" s="4"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="9"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="7"/>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A44" s="8" t="s">
+      <c r="A44" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B44" s="4"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="9"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="7"/>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A45" s="8" t="s">
+      <c r="A45" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B45" s="4"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="9"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="7"/>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A46" s="8" t="s">
+      <c r="A46" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B46" s="4"/>
-      <c r="C46" s="4"/>
-      <c r="D46" s="9"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="7"/>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A47" s="8" t="s">
+      <c r="A47" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B47" s="4"/>
-      <c r="C47" s="4"/>
-      <c r="D47" s="9"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="7"/>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A48" s="8" t="s">
+      <c r="A48" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B48" s="4"/>
-      <c r="C48" s="4"/>
-      <c r="D48" s="9"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="7"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A49" s="8" t="s">
+      <c r="A49" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B49" s="4"/>
-      <c r="C49" s="4"/>
-      <c r="D49" s="9"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="7"/>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A50" s="8" t="s">
+      <c r="A50" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B50" s="4"/>
-      <c r="C50" s="4"/>
-      <c r="D50" s="9"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="7"/>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A51" s="8" t="s">
+      <c r="A51" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B51" s="4"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="9"/>
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="7"/>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A52" s="8" t="s">
+      <c r="A52" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B52" s="4"/>
-      <c r="C52" s="4"/>
-      <c r="D52" s="9"/>
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="7"/>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A53" s="8" t="s">
+      <c r="A53" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B53" s="4"/>
-      <c r="C53" s="4"/>
-      <c r="D53" s="9"/>
+      <c r="B53" s="2"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="7"/>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A54" s="8" t="s">
+      <c r="A54" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B54" s="4"/>
-      <c r="C54" s="4"/>
-      <c r="D54" s="9"/>
+      <c r="B54" s="2"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="7"/>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A55" s="8" t="s">
+      <c r="A55" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B55" s="4"/>
-      <c r="C55" s="4"/>
-      <c r="D55" s="9"/>
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="7"/>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A56" s="8" t="s">
+      <c r="A56" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="B56" s="4"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="9"/>
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="7"/>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A57" s="8" t="s">
+      <c r="A57" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="B57" s="4"/>
-      <c r="C57" s="4"/>
-      <c r="D57" s="9"/>
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="7"/>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A58" s="8" t="s">
+      <c r="A58" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="B58" s="4"/>
-      <c r="C58" s="4"/>
-      <c r="D58" s="9"/>
+      <c r="B58" s="2"/>
+      <c r="C58" s="2"/>
+      <c r="D58" s="7"/>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A59" s="8" t="s">
+      <c r="A59" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B59" s="4"/>
-      <c r="C59" s="4"/>
-      <c r="D59" s="9"/>
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="7"/>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A60" s="8" t="s">
+      <c r="A60" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B60" s="4"/>
-      <c r="C60" s="4"/>
-      <c r="D60" s="9"/>
+      <c r="B60" s="2"/>
+      <c r="C60" s="2"/>
+      <c r="D60" s="7"/>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A61" s="8" t="s">
+      <c r="A61" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="B61" s="4"/>
-      <c r="C61" s="4"/>
-      <c r="D61" s="9"/>
+      <c r="B61" s="2"/>
+      <c r="C61" s="2"/>
+      <c r="D61" s="7"/>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A62" s="8" t="s">
+      <c r="A62" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B62" s="4"/>
-      <c r="C62" s="4"/>
-      <c r="D62" s="9"/>
+      <c r="B62" s="2"/>
+      <c r="C62" s="2"/>
+      <c r="D62" s="7"/>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A63" s="8" t="s">
+      <c r="A63" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B63" s="4"/>
-      <c r="C63" s="4"/>
-      <c r="D63" s="9"/>
+      <c r="B63" s="2"/>
+      <c r="C63" s="2"/>
+      <c r="D63" s="7"/>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A64" s="8" t="s">
+      <c r="A64" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="B64" s="4"/>
-      <c r="C64" s="4"/>
-      <c r="D64" s="9"/>
+      <c r="B64" s="2"/>
+      <c r="C64" s="2"/>
+      <c r="D64" s="7"/>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A65" s="8" t="s">
+      <c r="A65" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B65" s="4"/>
-      <c r="C65" s="4"/>
-      <c r="D65" s="9"/>
+      <c r="B65" s="2"/>
+      <c r="C65" s="2"/>
+      <c r="D65" s="7"/>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A66" s="8" t="s">
+      <c r="A66" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="B66" s="4"/>
-      <c r="C66" s="4"/>
-      <c r="D66" s="9"/>
+      <c r="B66" s="2"/>
+      <c r="C66" s="2"/>
+      <c r="D66" s="7"/>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A67" s="8" t="s">
+      <c r="A67" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B67" s="4"/>
-      <c r="C67" s="4"/>
-      <c r="D67" s="9"/>
+      <c r="B67" s="2"/>
+      <c r="C67" s="2"/>
+      <c r="D67" s="7"/>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A68" s="8" t="s">
+      <c r="A68" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B68" s="4"/>
-      <c r="C68" s="4"/>
-      <c r="D68" s="9"/>
+      <c r="B68" s="2"/>
+      <c r="C68" s="2"/>
+      <c r="D68" s="7"/>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A69" s="8" t="s">
+      <c r="A69" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="B69" s="4"/>
-      <c r="C69" s="4"/>
-      <c r="D69" s="9"/>
+      <c r="B69" s="2"/>
+      <c r="C69" s="2"/>
+      <c r="D69" s="7"/>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A70" s="8" t="s">
+      <c r="A70" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B70" s="4"/>
-      <c r="C70" s="4"/>
-      <c r="D70" s="9"/>
+      <c r="B70" s="2"/>
+      <c r="C70" s="2"/>
+      <c r="D70" s="7"/>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A71" s="8" t="s">
+      <c r="A71" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B71" s="4"/>
-      <c r="C71" s="4"/>
-      <c r="D71" s="9"/>
+      <c r="B71" s="2"/>
+      <c r="C71" s="2"/>
+      <c r="D71" s="7"/>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A72" s="8" t="s">
+      <c r="A72" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="B72" s="4"/>
-      <c r="C72" s="4"/>
-      <c r="D72" s="9"/>
+      <c r="B72" s="2"/>
+      <c r="C72" s="2"/>
+      <c r="D72" s="7"/>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A73" s="8" t="s">
+      <c r="A73" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="B73" s="4"/>
-      <c r="C73" s="4"/>
-      <c r="D73" s="9"/>
+      <c r="B73" s="2"/>
+      <c r="C73" s="2"/>
+      <c r="D73" s="7"/>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A74" s="8" t="s">
+      <c r="A74" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="B74" s="4"/>
-      <c r="C74" s="4"/>
-      <c r="D74" s="9"/>
+      <c r="B74" s="2"/>
+      <c r="C74" s="2"/>
+      <c r="D74" s="7"/>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A75" s="8" t="s">
+      <c r="A75" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="B75" s="4"/>
-      <c r="C75" s="4"/>
-      <c r="D75" s="9"/>
+      <c r="B75" s="2"/>
+      <c r="C75" s="2"/>
+      <c r="D75" s="7"/>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A76" s="8" t="s">
+      <c r="A76" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="B76" s="4"/>
-      <c r="C76" s="4"/>
-      <c r="D76" s="9"/>
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="7"/>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A77" s="8" t="s">
+      <c r="A77" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="B77" s="4"/>
-      <c r="C77" s="4"/>
-      <c r="D77" s="9"/>
+      <c r="B77" s="2"/>
+      <c r="C77" s="2"/>
+      <c r="D77" s="7"/>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A78" s="8" t="s">
+      <c r="A78" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="B78" s="4"/>
-      <c r="C78" s="4"/>
-      <c r="D78" s="9"/>
+      <c r="B78" s="2"/>
+      <c r="C78" s="2"/>
+      <c r="D78" s="7"/>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A79" s="8" t="s">
+      <c r="A79" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="B79" s="4"/>
-      <c r="C79" s="4"/>
-      <c r="D79" s="9"/>
+      <c r="B79" s="2"/>
+      <c r="C79" s="2"/>
+      <c r="D79" s="7"/>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A80" s="8" t="s">
+      <c r="A80" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="B80" s="4"/>
-      <c r="C80" s="4"/>
-      <c r="D80" s="9"/>
+      <c r="B80" s="2"/>
+      <c r="C80" s="2"/>
+      <c r="D80" s="7"/>
     </row>
     <row r="81" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A81" s="10">
+      <c r="A81" s="8">
         <v>46753</v>
       </c>
-      <c r="B81" s="11"/>
-      <c r="C81" s="11"/>
-      <c r="D81" s="12"/>
+      <c r="B81" s="9"/>
+      <c r="C81" s="9"/>
+      <c r="D81" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3091,658 +3529,658 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="5" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="9"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="7"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="9"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="7"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="9"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="7"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="9"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="7"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="9"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="7"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="9"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="7"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="9"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="7"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="9"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="7"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="9"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="7"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="9"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="7"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="9"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="7"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="9"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="7"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="9"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="7"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="9"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="7"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="9"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="7"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="9"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="7"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="9"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="7"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="9"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="7"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="9"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="7"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="9"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="7"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="9"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="7"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="9"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="7"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="9"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="7"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="9"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="7"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" s="8" t="s">
+      <c r="A26" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="9"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="7"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="9"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="7"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="9"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="7"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="9"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="7"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" s="8" t="s">
+      <c r="A30" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="9"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="7"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="9"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="7"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" s="8" t="s">
+      <c r="A32" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="9"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="7"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" s="8" t="s">
+      <c r="A33" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="9"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="7"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" s="8" t="s">
+      <c r="A34" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="9"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="7"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" s="8" t="s">
+      <c r="A35" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="9"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="7"/>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" s="8" t="s">
+      <c r="A36" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="9"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="7"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A37" s="8" t="s">
+      <c r="A37" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="9"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="7"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38" s="8" t="s">
+      <c r="A38" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="9"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="7"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39" s="8" t="s">
+      <c r="A39" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="9"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="7"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A40" s="8" t="s">
+      <c r="A40" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B40" s="4"/>
-      <c r="C40" s="4"/>
-      <c r="D40" s="9"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="7"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" s="8" t="s">
+      <c r="A41" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
-      <c r="D41" s="9"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="7"/>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42" s="8" t="s">
+      <c r="A42" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="9"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="7"/>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A43" s="8" t="s">
+      <c r="A43" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B43" s="4"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="9"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="7"/>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A44" s="8" t="s">
+      <c r="A44" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B44" s="4"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="9"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="7"/>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A45" s="8" t="s">
+      <c r="A45" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B45" s="4"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="9"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="7"/>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A46" s="8" t="s">
+      <c r="A46" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B46" s="4"/>
-      <c r="C46" s="4"/>
-      <c r="D46" s="9"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="7"/>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A47" s="8" t="s">
+      <c r="A47" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B47" s="4"/>
-      <c r="C47" s="4"/>
-      <c r="D47" s="9"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="7"/>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A48" s="8" t="s">
+      <c r="A48" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B48" s="4"/>
-      <c r="C48" s="4"/>
-      <c r="D48" s="9"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="7"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A49" s="8" t="s">
+      <c r="A49" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B49" s="4"/>
-      <c r="C49" s="4"/>
-      <c r="D49" s="9"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="7"/>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A50" s="8" t="s">
+      <c r="A50" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B50" s="4"/>
-      <c r="C50" s="4"/>
-      <c r="D50" s="9"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="7"/>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A51" s="8" t="s">
+      <c r="A51" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B51" s="4"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="9"/>
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="7"/>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A52" s="8" t="s">
+      <c r="A52" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B52" s="4"/>
-      <c r="C52" s="4"/>
-      <c r="D52" s="9"/>
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="7"/>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A53" s="8" t="s">
+      <c r="A53" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B53" s="4"/>
-      <c r="C53" s="4"/>
-      <c r="D53" s="9"/>
+      <c r="B53" s="2"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="7"/>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A54" s="8" t="s">
+      <c r="A54" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B54" s="4"/>
-      <c r="C54" s="4"/>
-      <c r="D54" s="9"/>
+      <c r="B54" s="2"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="7"/>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A55" s="8" t="s">
+      <c r="A55" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B55" s="4"/>
-      <c r="C55" s="4"/>
-      <c r="D55" s="9"/>
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="7"/>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A56" s="8" t="s">
+      <c r="A56" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="B56" s="4"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="9"/>
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="7"/>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A57" s="8" t="s">
+      <c r="A57" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="B57" s="4"/>
-      <c r="C57" s="4"/>
-      <c r="D57" s="9"/>
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="7"/>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A58" s="8" t="s">
+      <c r="A58" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="B58" s="4"/>
-      <c r="C58" s="4"/>
-      <c r="D58" s="9"/>
+      <c r="B58" s="2"/>
+      <c r="C58" s="2"/>
+      <c r="D58" s="7"/>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A59" s="8" t="s">
+      <c r="A59" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B59" s="4"/>
-      <c r="C59" s="4"/>
-      <c r="D59" s="9"/>
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="7"/>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A60" s="8" t="s">
+      <c r="A60" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B60" s="4"/>
-      <c r="C60" s="4"/>
-      <c r="D60" s="9"/>
+      <c r="B60" s="2"/>
+      <c r="C60" s="2"/>
+      <c r="D60" s="7"/>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A61" s="8" t="s">
+      <c r="A61" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="B61" s="4"/>
-      <c r="C61" s="4"/>
-      <c r="D61" s="9"/>
+      <c r="B61" s="2"/>
+      <c r="C61" s="2"/>
+      <c r="D61" s="7"/>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A62" s="8" t="s">
+      <c r="A62" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B62" s="4"/>
-      <c r="C62" s="4"/>
-      <c r="D62" s="9"/>
+      <c r="B62" s="2"/>
+      <c r="C62" s="2"/>
+      <c r="D62" s="7"/>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A63" s="8" t="s">
+      <c r="A63" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B63" s="4"/>
-      <c r="C63" s="4"/>
-      <c r="D63" s="9"/>
+      <c r="B63" s="2"/>
+      <c r="C63" s="2"/>
+      <c r="D63" s="7"/>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A64" s="8" t="s">
+      <c r="A64" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="B64" s="4"/>
-      <c r="C64" s="4"/>
-      <c r="D64" s="9"/>
+      <c r="B64" s="2"/>
+      <c r="C64" s="2"/>
+      <c r="D64" s="7"/>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A65" s="8" t="s">
+      <c r="A65" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B65" s="4"/>
-      <c r="C65" s="4"/>
-      <c r="D65" s="9"/>
+      <c r="B65" s="2"/>
+      <c r="C65" s="2"/>
+      <c r="D65" s="7"/>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A66" s="8" t="s">
+      <c r="A66" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="B66" s="4"/>
-      <c r="C66" s="4"/>
-      <c r="D66" s="9"/>
+      <c r="B66" s="2"/>
+      <c r="C66" s="2"/>
+      <c r="D66" s="7"/>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A67" s="8" t="s">
+      <c r="A67" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B67" s="4"/>
-      <c r="C67" s="4"/>
-      <c r="D67" s="9"/>
+      <c r="B67" s="2"/>
+      <c r="C67" s="2"/>
+      <c r="D67" s="7"/>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A68" s="8" t="s">
+      <c r="A68" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B68" s="4"/>
-      <c r="C68" s="4"/>
-      <c r="D68" s="9"/>
+      <c r="B68" s="2"/>
+      <c r="C68" s="2"/>
+      <c r="D68" s="7"/>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A69" s="8" t="s">
+      <c r="A69" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="B69" s="4"/>
-      <c r="C69" s="4"/>
-      <c r="D69" s="9"/>
+      <c r="B69" s="2"/>
+      <c r="C69" s="2"/>
+      <c r="D69" s="7"/>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A70" s="8" t="s">
+      <c r="A70" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B70" s="4"/>
-      <c r="C70" s="4"/>
-      <c r="D70" s="9"/>
+      <c r="B70" s="2"/>
+      <c r="C70" s="2"/>
+      <c r="D70" s="7"/>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A71" s="8" t="s">
+      <c r="A71" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B71" s="4"/>
-      <c r="C71" s="4"/>
-      <c r="D71" s="9"/>
+      <c r="B71" s="2"/>
+      <c r="C71" s="2"/>
+      <c r="D71" s="7"/>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A72" s="8" t="s">
+      <c r="A72" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="B72" s="4"/>
-      <c r="C72" s="4"/>
-      <c r="D72" s="9"/>
+      <c r="B72" s="2"/>
+      <c r="C72" s="2"/>
+      <c r="D72" s="7"/>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A73" s="8" t="s">
+      <c r="A73" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="B73" s="4"/>
-      <c r="C73" s="4"/>
-      <c r="D73" s="9"/>
+      <c r="B73" s="2"/>
+      <c r="C73" s="2"/>
+      <c r="D73" s="7"/>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A74" s="8" t="s">
+      <c r="A74" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="B74" s="4"/>
-      <c r="C74" s="4"/>
-      <c r="D74" s="9"/>
+      <c r="B74" s="2"/>
+      <c r="C74" s="2"/>
+      <c r="D74" s="7"/>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A75" s="8" t="s">
+      <c r="A75" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="B75" s="4"/>
-      <c r="C75" s="4"/>
-      <c r="D75" s="9"/>
+      <c r="B75" s="2"/>
+      <c r="C75" s="2"/>
+      <c r="D75" s="7"/>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A76" s="8" t="s">
+      <c r="A76" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="B76" s="4"/>
-      <c r="C76" s="4"/>
-      <c r="D76" s="9"/>
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="7"/>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A77" s="8" t="s">
+      <c r="A77" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="B77" s="4"/>
-      <c r="C77" s="4"/>
-      <c r="D77" s="9"/>
+      <c r="B77" s="2"/>
+      <c r="C77" s="2"/>
+      <c r="D77" s="7"/>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A78" s="8" t="s">
+      <c r="A78" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="B78" s="4"/>
-      <c r="C78" s="4"/>
-      <c r="D78" s="9"/>
+      <c r="B78" s="2"/>
+      <c r="C78" s="2"/>
+      <c r="D78" s="7"/>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A79" s="8" t="s">
+      <c r="A79" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="B79" s="4"/>
-      <c r="C79" s="4"/>
-      <c r="D79" s="9"/>
+      <c r="B79" s="2"/>
+      <c r="C79" s="2"/>
+      <c r="D79" s="7"/>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A80" s="8" t="s">
+      <c r="A80" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="B80" s="4"/>
-      <c r="C80" s="4"/>
-      <c r="D80" s="9"/>
+      <c r="B80" s="2"/>
+      <c r="C80" s="2"/>
+      <c r="D80" s="7"/>
     </row>
     <row r="81" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A81" s="10">
+      <c r="A81" s="8">
         <v>46753</v>
       </c>
-      <c r="B81" s="11"/>
-      <c r="C81" s="11"/>
-      <c r="D81" s="12"/>
+      <c r="B81" s="9"/>
+      <c r="C81" s="9"/>
+      <c r="D81" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3761,658 +4199,658 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="5" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="9"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="7"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="9"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="7"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="9"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="7"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="9"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="7"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="9"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="7"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="9"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="7"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="9"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="7"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="9"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="7"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="9"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="7"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="9"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="7"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="9"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="7"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="9"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="7"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="9"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="7"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="9"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="7"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="9"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="7"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="9"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="7"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="9"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="7"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="9"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="7"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="9"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="7"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="9"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="7"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="9"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="7"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="9"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="7"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="9"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="7"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="9"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="7"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" s="8" t="s">
+      <c r="A26" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="9"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="7"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="9"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="7"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="9"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="7"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="9"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="7"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" s="8" t="s">
+      <c r="A30" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="9"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="7"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="9"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="7"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" s="8" t="s">
+      <c r="A32" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="9"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="7"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" s="8" t="s">
+      <c r="A33" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="9"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="7"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" s="8" t="s">
+      <c r="A34" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="9"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="7"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" s="8" t="s">
+      <c r="A35" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="9"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="7"/>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" s="8" t="s">
+      <c r="A36" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="9"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="7"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A37" s="8" t="s">
+      <c r="A37" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="9"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="7"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38" s="8" t="s">
+      <c r="A38" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="9"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="7"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39" s="8" t="s">
+      <c r="A39" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="9"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="7"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A40" s="8" t="s">
+      <c r="A40" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B40" s="4"/>
-      <c r="C40" s="4"/>
-      <c r="D40" s="9"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="7"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" s="8" t="s">
+      <c r="A41" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
-      <c r="D41" s="9"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="7"/>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42" s="8" t="s">
+      <c r="A42" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="9"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="7"/>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A43" s="8" t="s">
+      <c r="A43" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B43" s="4"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="9"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="7"/>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A44" s="8" t="s">
+      <c r="A44" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B44" s="4"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="9"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="7"/>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A45" s="8" t="s">
+      <c r="A45" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B45" s="4"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="9"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="7"/>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A46" s="8" t="s">
+      <c r="A46" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B46" s="4"/>
-      <c r="C46" s="4"/>
-      <c r="D46" s="9"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="7"/>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A47" s="8" t="s">
+      <c r="A47" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B47" s="4"/>
-      <c r="C47" s="4"/>
-      <c r="D47" s="9"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="7"/>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A48" s="8" t="s">
+      <c r="A48" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B48" s="4"/>
-      <c r="C48" s="4"/>
-      <c r="D48" s="9"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="7"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A49" s="8" t="s">
+      <c r="A49" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B49" s="4"/>
-      <c r="C49" s="4"/>
-      <c r="D49" s="9"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="7"/>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A50" s="8" t="s">
+      <c r="A50" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B50" s="4"/>
-      <c r="C50" s="4"/>
-      <c r="D50" s="9"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="7"/>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A51" s="8" t="s">
+      <c r="A51" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B51" s="4"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="9"/>
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="7"/>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A52" s="8" t="s">
+      <c r="A52" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B52" s="4"/>
-      <c r="C52" s="4"/>
-      <c r="D52" s="9"/>
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="7"/>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A53" s="8" t="s">
+      <c r="A53" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B53" s="4"/>
-      <c r="C53" s="4"/>
-      <c r="D53" s="9"/>
+      <c r="B53" s="2"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="7"/>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A54" s="8" t="s">
+      <c r="A54" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B54" s="4"/>
-      <c r="C54" s="4"/>
-      <c r="D54" s="9"/>
+      <c r="B54" s="2"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="7"/>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A55" s="8" t="s">
+      <c r="A55" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B55" s="4"/>
-      <c r="C55" s="4"/>
-      <c r="D55" s="9"/>
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="7"/>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A56" s="8" t="s">
+      <c r="A56" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="B56" s="4"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="9"/>
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="7"/>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A57" s="8" t="s">
+      <c r="A57" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="B57" s="4"/>
-      <c r="C57" s="4"/>
-      <c r="D57" s="9"/>
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="7"/>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A58" s="8" t="s">
+      <c r="A58" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="B58" s="4"/>
-      <c r="C58" s="4"/>
-      <c r="D58" s="9"/>
+      <c r="B58" s="2"/>
+      <c r="C58" s="2"/>
+      <c r="D58" s="7"/>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A59" s="8" t="s">
+      <c r="A59" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B59" s="4"/>
-      <c r="C59" s="4"/>
-      <c r="D59" s="9"/>
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="7"/>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A60" s="8" t="s">
+      <c r="A60" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B60" s="4"/>
-      <c r="C60" s="4"/>
-      <c r="D60" s="9"/>
+      <c r="B60" s="2"/>
+      <c r="C60" s="2"/>
+      <c r="D60" s="7"/>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A61" s="8" t="s">
+      <c r="A61" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="B61" s="4"/>
-      <c r="C61" s="4"/>
-      <c r="D61" s="9"/>
+      <c r="B61" s="2"/>
+      <c r="C61" s="2"/>
+      <c r="D61" s="7"/>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A62" s="8" t="s">
+      <c r="A62" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B62" s="4"/>
-      <c r="C62" s="4"/>
-      <c r="D62" s="9"/>
+      <c r="B62" s="2"/>
+      <c r="C62" s="2"/>
+      <c r="D62" s="7"/>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A63" s="8" t="s">
+      <c r="A63" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B63" s="4"/>
-      <c r="C63" s="4"/>
-      <c r="D63" s="9"/>
+      <c r="B63" s="2"/>
+      <c r="C63" s="2"/>
+      <c r="D63" s="7"/>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A64" s="8" t="s">
+      <c r="A64" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="B64" s="4"/>
-      <c r="C64" s="4"/>
-      <c r="D64" s="9"/>
+      <c r="B64" s="2"/>
+      <c r="C64" s="2"/>
+      <c r="D64" s="7"/>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A65" s="8" t="s">
+      <c r="A65" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B65" s="4"/>
-      <c r="C65" s="4"/>
-      <c r="D65" s="9"/>
+      <c r="B65" s="2"/>
+      <c r="C65" s="2"/>
+      <c r="D65" s="7"/>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A66" s="8" t="s">
+      <c r="A66" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="B66" s="4"/>
-      <c r="C66" s="4"/>
-      <c r="D66" s="9"/>
+      <c r="B66" s="2"/>
+      <c r="C66" s="2"/>
+      <c r="D66" s="7"/>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A67" s="8" t="s">
+      <c r="A67" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B67" s="4"/>
-      <c r="C67" s="4"/>
-      <c r="D67" s="9"/>
+      <c r="B67" s="2"/>
+      <c r="C67" s="2"/>
+      <c r="D67" s="7"/>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A68" s="8" t="s">
+      <c r="A68" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B68" s="4"/>
-      <c r="C68" s="4"/>
-      <c r="D68" s="9"/>
+      <c r="B68" s="2"/>
+      <c r="C68" s="2"/>
+      <c r="D68" s="7"/>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A69" s="8" t="s">
+      <c r="A69" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="B69" s="4"/>
-      <c r="C69" s="4"/>
-      <c r="D69" s="9"/>
+      <c r="B69" s="2"/>
+      <c r="C69" s="2"/>
+      <c r="D69" s="7"/>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A70" s="8" t="s">
+      <c r="A70" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B70" s="4"/>
-      <c r="C70" s="4"/>
-      <c r="D70" s="9"/>
+      <c r="B70" s="2"/>
+      <c r="C70" s="2"/>
+      <c r="D70" s="7"/>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A71" s="8" t="s">
+      <c r="A71" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B71" s="4"/>
-      <c r="C71" s="4"/>
-      <c r="D71" s="9"/>
+      <c r="B71" s="2"/>
+      <c r="C71" s="2"/>
+      <c r="D71" s="7"/>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A72" s="8" t="s">
+      <c r="A72" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="B72" s="4"/>
-      <c r="C72" s="4"/>
-      <c r="D72" s="9"/>
+      <c r="B72" s="2"/>
+      <c r="C72" s="2"/>
+      <c r="D72" s="7"/>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A73" s="8" t="s">
+      <c r="A73" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="B73" s="4"/>
-      <c r="C73" s="4"/>
-      <c r="D73" s="9"/>
+      <c r="B73" s="2"/>
+      <c r="C73" s="2"/>
+      <c r="D73" s="7"/>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A74" s="8" t="s">
+      <c r="A74" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="B74" s="4"/>
-      <c r="C74" s="4"/>
-      <c r="D74" s="9"/>
+      <c r="B74" s="2"/>
+      <c r="C74" s="2"/>
+      <c r="D74" s="7"/>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A75" s="8" t="s">
+      <c r="A75" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="B75" s="4"/>
-      <c r="C75" s="4"/>
-      <c r="D75" s="9"/>
+      <c r="B75" s="2"/>
+      <c r="C75" s="2"/>
+      <c r="D75" s="7"/>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A76" s="8" t="s">
+      <c r="A76" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="B76" s="4"/>
-      <c r="C76" s="4"/>
-      <c r="D76" s="9"/>
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="7"/>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A77" s="8" t="s">
+      <c r="A77" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="B77" s="4"/>
-      <c r="C77" s="4"/>
-      <c r="D77" s="9"/>
+      <c r="B77" s="2"/>
+      <c r="C77" s="2"/>
+      <c r="D77" s="7"/>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A78" s="8" t="s">
+      <c r="A78" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="B78" s="4"/>
-      <c r="C78" s="4"/>
-      <c r="D78" s="9"/>
+      <c r="B78" s="2"/>
+      <c r="C78" s="2"/>
+      <c r="D78" s="7"/>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A79" s="8" t="s">
+      <c r="A79" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="B79" s="4"/>
-      <c r="C79" s="4"/>
-      <c r="D79" s="9"/>
+      <c r="B79" s="2"/>
+      <c r="C79" s="2"/>
+      <c r="D79" s="7"/>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A80" s="8" t="s">
+      <c r="A80" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="B80" s="4"/>
-      <c r="C80" s="4"/>
-      <c r="D80" s="9"/>
+      <c r="B80" s="2"/>
+      <c r="C80" s="2"/>
+      <c r="D80" s="7"/>
     </row>
     <row r="81" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A81" s="10">
+      <c r="A81" s="8">
         <v>46753</v>
       </c>
-      <c r="B81" s="11"/>
-      <c r="C81" s="11"/>
-      <c r="D81" s="12"/>
+      <c r="B81" s="9"/>
+      <c r="C81" s="9"/>
+      <c r="D81" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4431,658 +4869,658 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="5" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="9"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="7"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="9"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="7"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="9"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="7"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="9"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="7"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="9"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="7"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="9"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="7"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="9"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="7"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="9"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="7"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="9"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="7"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="9"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="7"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="9"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="7"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="9"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="7"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="9"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="7"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="9"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="7"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="9"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="7"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="9"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="7"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="9"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="7"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="9"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="7"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="9"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="7"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="9"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="7"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="9"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="7"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="9"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="7"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="9"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="7"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="9"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="7"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" s="8" t="s">
+      <c r="A26" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="9"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="7"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="9"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="7"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="9"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="7"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="9"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="7"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" s="8" t="s">
+      <c r="A30" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="9"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="7"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="9"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="7"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" s="8" t="s">
+      <c r="A32" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="9"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="7"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" s="8" t="s">
+      <c r="A33" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="9"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="7"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" s="8" t="s">
+      <c r="A34" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="9"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="7"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" s="8" t="s">
+      <c r="A35" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="9"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="7"/>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" s="8" t="s">
+      <c r="A36" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="9"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="7"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A37" s="8" t="s">
+      <c r="A37" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="9"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="7"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38" s="8" t="s">
+      <c r="A38" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="9"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="7"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39" s="8" t="s">
+      <c r="A39" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="9"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="7"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A40" s="8" t="s">
+      <c r="A40" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B40" s="4"/>
-      <c r="C40" s="4"/>
-      <c r="D40" s="9"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="7"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" s="8" t="s">
+      <c r="A41" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
-      <c r="D41" s="9"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="7"/>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42" s="8" t="s">
+      <c r="A42" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="9"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="7"/>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A43" s="8" t="s">
+      <c r="A43" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B43" s="4"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="9"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="7"/>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A44" s="8" t="s">
+      <c r="A44" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B44" s="4"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="9"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="7"/>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A45" s="8" t="s">
+      <c r="A45" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B45" s="4"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="9"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="7"/>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A46" s="8" t="s">
+      <c r="A46" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B46" s="4"/>
-      <c r="C46" s="4"/>
-      <c r="D46" s="9"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="7"/>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A47" s="8" t="s">
+      <c r="A47" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B47" s="4"/>
-      <c r="C47" s="4"/>
-      <c r="D47" s="9"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="7"/>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A48" s="8" t="s">
+      <c r="A48" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B48" s="4"/>
-      <c r="C48" s="4"/>
-      <c r="D48" s="9"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="7"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A49" s="8" t="s">
+      <c r="A49" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B49" s="4"/>
-      <c r="C49" s="4"/>
-      <c r="D49" s="9"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="7"/>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A50" s="8" t="s">
+      <c r="A50" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B50" s="4"/>
-      <c r="C50" s="4"/>
-      <c r="D50" s="9"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="7"/>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A51" s="8" t="s">
+      <c r="A51" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B51" s="4"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="9"/>
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="7"/>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A52" s="8" t="s">
+      <c r="A52" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B52" s="4"/>
-      <c r="C52" s="4"/>
-      <c r="D52" s="9"/>
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="7"/>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A53" s="8" t="s">
+      <c r="A53" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B53" s="4"/>
-      <c r="C53" s="4"/>
-      <c r="D53" s="9"/>
+      <c r="B53" s="2"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="7"/>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A54" s="8" t="s">
+      <c r="A54" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B54" s="4"/>
-      <c r="C54" s="4"/>
-      <c r="D54" s="9"/>
+      <c r="B54" s="2"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="7"/>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A55" s="8" t="s">
+      <c r="A55" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B55" s="4"/>
-      <c r="C55" s="4"/>
-      <c r="D55" s="9"/>
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="7"/>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A56" s="8" t="s">
+      <c r="A56" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="B56" s="4"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="9"/>
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="7"/>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A57" s="8" t="s">
+      <c r="A57" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="B57" s="4"/>
-      <c r="C57" s="4"/>
-      <c r="D57" s="9"/>
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="7"/>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A58" s="8" t="s">
+      <c r="A58" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="B58" s="4"/>
-      <c r="C58" s="4"/>
-      <c r="D58" s="9"/>
+      <c r="B58" s="2"/>
+      <c r="C58" s="2"/>
+      <c r="D58" s="7"/>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A59" s="8" t="s">
+      <c r="A59" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B59" s="4"/>
-      <c r="C59" s="4"/>
-      <c r="D59" s="9"/>
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="7"/>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A60" s="8" t="s">
+      <c r="A60" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B60" s="4"/>
-      <c r="C60" s="4"/>
-      <c r="D60" s="9"/>
+      <c r="B60" s="2"/>
+      <c r="C60" s="2"/>
+      <c r="D60" s="7"/>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A61" s="8" t="s">
+      <c r="A61" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="B61" s="4"/>
-      <c r="C61" s="4"/>
-      <c r="D61" s="9"/>
+      <c r="B61" s="2"/>
+      <c r="C61" s="2"/>
+      <c r="D61" s="7"/>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A62" s="8" t="s">
+      <c r="A62" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B62" s="4"/>
-      <c r="C62" s="4"/>
-      <c r="D62" s="9"/>
+      <c r="B62" s="2"/>
+      <c r="C62" s="2"/>
+      <c r="D62" s="7"/>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A63" s="8" t="s">
+      <c r="A63" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B63" s="4"/>
-      <c r="C63" s="4"/>
-      <c r="D63" s="9"/>
+      <c r="B63" s="2"/>
+      <c r="C63" s="2"/>
+      <c r="D63" s="7"/>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A64" s="8" t="s">
+      <c r="A64" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="B64" s="4"/>
-      <c r="C64" s="4"/>
-      <c r="D64" s="9"/>
+      <c r="B64" s="2"/>
+      <c r="C64" s="2"/>
+      <c r="D64" s="7"/>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A65" s="8" t="s">
+      <c r="A65" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B65" s="4"/>
-      <c r="C65" s="4"/>
-      <c r="D65" s="9"/>
+      <c r="B65" s="2"/>
+      <c r="C65" s="2"/>
+      <c r="D65" s="7"/>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A66" s="8" t="s">
+      <c r="A66" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="B66" s="4"/>
-      <c r="C66" s="4"/>
-      <c r="D66" s="9"/>
+      <c r="B66" s="2"/>
+      <c r="C66" s="2"/>
+      <c r="D66" s="7"/>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A67" s="8" t="s">
+      <c r="A67" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B67" s="4"/>
-      <c r="C67" s="4"/>
-      <c r="D67" s="9"/>
+      <c r="B67" s="2"/>
+      <c r="C67" s="2"/>
+      <c r="D67" s="7"/>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A68" s="8" t="s">
+      <c r="A68" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B68" s="4"/>
-      <c r="C68" s="4"/>
-      <c r="D68" s="9"/>
+      <c r="B68" s="2"/>
+      <c r="C68" s="2"/>
+      <c r="D68" s="7"/>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A69" s="8" t="s">
+      <c r="A69" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="B69" s="4"/>
-      <c r="C69" s="4"/>
-      <c r="D69" s="9"/>
+      <c r="B69" s="2"/>
+      <c r="C69" s="2"/>
+      <c r="D69" s="7"/>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A70" s="8" t="s">
+      <c r="A70" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B70" s="4"/>
-      <c r="C70" s="4"/>
-      <c r="D70" s="9"/>
+      <c r="B70" s="2"/>
+      <c r="C70" s="2"/>
+      <c r="D70" s="7"/>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A71" s="8" t="s">
+      <c r="A71" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B71" s="4"/>
-      <c r="C71" s="4"/>
-      <c r="D71" s="9"/>
+      <c r="B71" s="2"/>
+      <c r="C71" s="2"/>
+      <c r="D71" s="7"/>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A72" s="8" t="s">
+      <c r="A72" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="B72" s="4"/>
-      <c r="C72" s="4"/>
-      <c r="D72" s="9"/>
+      <c r="B72" s="2"/>
+      <c r="C72" s="2"/>
+      <c r="D72" s="7"/>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A73" s="8" t="s">
+      <c r="A73" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="B73" s="4"/>
-      <c r="C73" s="4"/>
-      <c r="D73" s="9"/>
+      <c r="B73" s="2"/>
+      <c r="C73" s="2"/>
+      <c r="D73" s="7"/>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A74" s="8" t="s">
+      <c r="A74" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="B74" s="4"/>
-      <c r="C74" s="4"/>
-      <c r="D74" s="9"/>
+      <c r="B74" s="2"/>
+      <c r="C74" s="2"/>
+      <c r="D74" s="7"/>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A75" s="8" t="s">
+      <c r="A75" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="B75" s="4"/>
-      <c r="C75" s="4"/>
-      <c r="D75" s="9"/>
+      <c r="B75" s="2"/>
+      <c r="C75" s="2"/>
+      <c r="D75" s="7"/>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A76" s="8" t="s">
+      <c r="A76" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="B76" s="4"/>
-      <c r="C76" s="4"/>
-      <c r="D76" s="9"/>
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="7"/>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A77" s="8" t="s">
+      <c r="A77" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="B77" s="4"/>
-      <c r="C77" s="4"/>
-      <c r="D77" s="9"/>
+      <c r="B77" s="2"/>
+      <c r="C77" s="2"/>
+      <c r="D77" s="7"/>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A78" s="8" t="s">
+      <c r="A78" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="B78" s="4"/>
-      <c r="C78" s="4"/>
-      <c r="D78" s="9"/>
+      <c r="B78" s="2"/>
+      <c r="C78" s="2"/>
+      <c r="D78" s="7"/>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A79" s="8" t="s">
+      <c r="A79" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="B79" s="4"/>
-      <c r="C79" s="4"/>
-      <c r="D79" s="9"/>
+      <c r="B79" s="2"/>
+      <c r="C79" s="2"/>
+      <c r="D79" s="7"/>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A80" s="8" t="s">
+      <c r="A80" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="B80" s="4"/>
-      <c r="C80" s="4"/>
-      <c r="D80" s="9"/>
+      <c r="B80" s="2"/>
+      <c r="C80" s="2"/>
+      <c r="D80" s="7"/>
     </row>
     <row r="81" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A81" s="10">
+      <c r="A81" s="8">
         <v>46753</v>
       </c>
-      <c r="B81" s="11"/>
-      <c r="C81" s="11"/>
-      <c r="D81" s="12"/>
+      <c r="B81" s="9"/>
+      <c r="C81" s="9"/>
+      <c r="D81" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5101,658 +5539,658 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="5" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="9"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="7"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="9"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="7"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="9"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="7"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="9"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="7"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="9"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="7"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="9"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="7"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="9"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="7"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="9"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="7"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="9"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="7"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="9"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="7"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="9"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="7"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="9"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="7"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="9"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="7"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="9"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="7"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="9"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="7"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="9"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="7"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="9"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="7"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="9"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="7"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="9"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="7"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="9"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="7"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="9"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="7"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="9"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="7"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="9"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="7"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="9"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="7"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" s="8" t="s">
+      <c r="A26" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="9"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="7"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="9"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="7"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="9"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="7"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="9"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="7"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" s="8" t="s">
+      <c r="A30" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="9"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="7"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="9"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="7"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" s="8" t="s">
+      <c r="A32" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="9"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="7"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" s="8" t="s">
+      <c r="A33" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="9"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="7"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" s="8" t="s">
+      <c r="A34" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="9"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="7"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" s="8" t="s">
+      <c r="A35" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="9"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="7"/>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" s="8" t="s">
+      <c r="A36" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="9"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="7"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A37" s="8" t="s">
+      <c r="A37" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="9"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="7"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38" s="8" t="s">
+      <c r="A38" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="9"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="7"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39" s="8" t="s">
+      <c r="A39" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="9"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="7"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A40" s="8" t="s">
+      <c r="A40" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B40" s="4"/>
-      <c r="C40" s="4"/>
-      <c r="D40" s="9"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="7"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" s="8" t="s">
+      <c r="A41" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
-      <c r="D41" s="9"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="7"/>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42" s="8" t="s">
+      <c r="A42" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="9"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="7"/>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A43" s="8" t="s">
+      <c r="A43" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B43" s="4"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="9"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="7"/>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A44" s="8" t="s">
+      <c r="A44" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B44" s="4"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="9"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="7"/>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A45" s="8" t="s">
+      <c r="A45" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B45" s="4"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="9"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="7"/>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A46" s="8" t="s">
+      <c r="A46" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B46" s="4"/>
-      <c r="C46" s="4"/>
-      <c r="D46" s="9"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="7"/>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A47" s="8" t="s">
+      <c r="A47" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B47" s="4"/>
-      <c r="C47" s="4"/>
-      <c r="D47" s="9"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="7"/>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A48" s="8" t="s">
+      <c r="A48" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B48" s="4"/>
-      <c r="C48" s="4"/>
-      <c r="D48" s="9"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="7"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A49" s="8" t="s">
+      <c r="A49" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B49" s="4"/>
-      <c r="C49" s="4"/>
-      <c r="D49" s="9"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="7"/>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A50" s="8" t="s">
+      <c r="A50" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B50" s="4"/>
-      <c r="C50" s="4"/>
-      <c r="D50" s="9"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="7"/>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A51" s="8" t="s">
+      <c r="A51" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B51" s="4"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="9"/>
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="7"/>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A52" s="8" t="s">
+      <c r="A52" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B52" s="4"/>
-      <c r="C52" s="4"/>
-      <c r="D52" s="9"/>
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="7"/>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A53" s="8" t="s">
+      <c r="A53" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B53" s="4"/>
-      <c r="C53" s="4"/>
-      <c r="D53" s="9"/>
+      <c r="B53" s="2"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="7"/>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A54" s="8" t="s">
+      <c r="A54" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B54" s="4"/>
-      <c r="C54" s="4"/>
-      <c r="D54" s="9"/>
+      <c r="B54" s="2"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="7"/>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A55" s="8" t="s">
+      <c r="A55" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B55" s="4"/>
-      <c r="C55" s="4"/>
-      <c r="D55" s="9"/>
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="7"/>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A56" s="8" t="s">
+      <c r="A56" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="B56" s="4"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="9"/>
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="7"/>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A57" s="8" t="s">
+      <c r="A57" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="B57" s="4"/>
-      <c r="C57" s="4"/>
-      <c r="D57" s="9"/>
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="7"/>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A58" s="8" t="s">
+      <c r="A58" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="B58" s="4"/>
-      <c r="C58" s="4"/>
-      <c r="D58" s="9"/>
+      <c r="B58" s="2"/>
+      <c r="C58" s="2"/>
+      <c r="D58" s="7"/>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A59" s="8" t="s">
+      <c r="A59" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B59" s="4"/>
-      <c r="C59" s="4"/>
-      <c r="D59" s="9"/>
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="7"/>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A60" s="8" t="s">
+      <c r="A60" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B60" s="4"/>
-      <c r="C60" s="4"/>
-      <c r="D60" s="9"/>
+      <c r="B60" s="2"/>
+      <c r="C60" s="2"/>
+      <c r="D60" s="7"/>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A61" s="8" t="s">
+      <c r="A61" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="B61" s="4"/>
-      <c r="C61" s="4"/>
-      <c r="D61" s="9"/>
+      <c r="B61" s="2"/>
+      <c r="C61" s="2"/>
+      <c r="D61" s="7"/>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A62" s="8" t="s">
+      <c r="A62" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B62" s="4"/>
-      <c r="C62" s="4"/>
-      <c r="D62" s="9"/>
+      <c r="B62" s="2"/>
+      <c r="C62" s="2"/>
+      <c r="D62" s="7"/>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A63" s="8" t="s">
+      <c r="A63" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B63" s="4"/>
-      <c r="C63" s="4"/>
-      <c r="D63" s="9"/>
+      <c r="B63" s="2"/>
+      <c r="C63" s="2"/>
+      <c r="D63" s="7"/>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A64" s="8" t="s">
+      <c r="A64" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="B64" s="4"/>
-      <c r="C64" s="4"/>
-      <c r="D64" s="9"/>
+      <c r="B64" s="2"/>
+      <c r="C64" s="2"/>
+      <c r="D64" s="7"/>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A65" s="8" t="s">
+      <c r="A65" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B65" s="4"/>
-      <c r="C65" s="4"/>
-      <c r="D65" s="9"/>
+      <c r="B65" s="2"/>
+      <c r="C65" s="2"/>
+      <c r="D65" s="7"/>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A66" s="8" t="s">
+      <c r="A66" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="B66" s="4"/>
-      <c r="C66" s="4"/>
-      <c r="D66" s="9"/>
+      <c r="B66" s="2"/>
+      <c r="C66" s="2"/>
+      <c r="D66" s="7"/>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A67" s="8" t="s">
+      <c r="A67" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B67" s="4"/>
-      <c r="C67" s="4"/>
-      <c r="D67" s="9"/>
+      <c r="B67" s="2"/>
+      <c r="C67" s="2"/>
+      <c r="D67" s="7"/>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A68" s="8" t="s">
+      <c r="A68" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B68" s="4"/>
-      <c r="C68" s="4"/>
-      <c r="D68" s="9"/>
+      <c r="B68" s="2"/>
+      <c r="C68" s="2"/>
+      <c r="D68" s="7"/>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A69" s="8" t="s">
+      <c r="A69" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="B69" s="4"/>
-      <c r="C69" s="4"/>
-      <c r="D69" s="9"/>
+      <c r="B69" s="2"/>
+      <c r="C69" s="2"/>
+      <c r="D69" s="7"/>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A70" s="8" t="s">
+      <c r="A70" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B70" s="4"/>
-      <c r="C70" s="4"/>
-      <c r="D70" s="9"/>
+      <c r="B70" s="2"/>
+      <c r="C70" s="2"/>
+      <c r="D70" s="7"/>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A71" s="8" t="s">
+      <c r="A71" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B71" s="4"/>
-      <c r="C71" s="4"/>
-      <c r="D71" s="9"/>
+      <c r="B71" s="2"/>
+      <c r="C71" s="2"/>
+      <c r="D71" s="7"/>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A72" s="8" t="s">
+      <c r="A72" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="B72" s="4"/>
-      <c r="C72" s="4"/>
-      <c r="D72" s="9"/>
+      <c r="B72" s="2"/>
+      <c r="C72" s="2"/>
+      <c r="D72" s="7"/>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A73" s="8" t="s">
+      <c r="A73" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="B73" s="4"/>
-      <c r="C73" s="4"/>
-      <c r="D73" s="9"/>
+      <c r="B73" s="2"/>
+      <c r="C73" s="2"/>
+      <c r="D73" s="7"/>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A74" s="8" t="s">
+      <c r="A74" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="B74" s="4"/>
-      <c r="C74" s="4"/>
-      <c r="D74" s="9"/>
+      <c r="B74" s="2"/>
+      <c r="C74" s="2"/>
+      <c r="D74" s="7"/>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A75" s="8" t="s">
+      <c r="A75" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="B75" s="4"/>
-      <c r="C75" s="4"/>
-      <c r="D75" s="9"/>
+      <c r="B75" s="2"/>
+      <c r="C75" s="2"/>
+      <c r="D75" s="7"/>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A76" s="8" t="s">
+      <c r="A76" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="B76" s="4"/>
-      <c r="C76" s="4"/>
-      <c r="D76" s="9"/>
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="7"/>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A77" s="8" t="s">
+      <c r="A77" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="B77" s="4"/>
-      <c r="C77" s="4"/>
-      <c r="D77" s="9"/>
+      <c r="B77" s="2"/>
+      <c r="C77" s="2"/>
+      <c r="D77" s="7"/>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A78" s="8" t="s">
+      <c r="A78" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="B78" s="4"/>
-      <c r="C78" s="4"/>
-      <c r="D78" s="9"/>
+      <c r="B78" s="2"/>
+      <c r="C78" s="2"/>
+      <c r="D78" s="7"/>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A79" s="8" t="s">
+      <c r="A79" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="B79" s="4"/>
-      <c r="C79" s="4"/>
-      <c r="D79" s="9"/>
+      <c r="B79" s="2"/>
+      <c r="C79" s="2"/>
+      <c r="D79" s="7"/>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A80" s="8" t="s">
+      <c r="A80" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="B80" s="4"/>
-      <c r="C80" s="4"/>
-      <c r="D80" s="9"/>
+      <c r="B80" s="2"/>
+      <c r="C80" s="2"/>
+      <c r="D80" s="7"/>
     </row>
     <row r="81" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A81" s="10">
+      <c r="A81" s="8">
         <v>46753</v>
       </c>
-      <c r="B81" s="11"/>
-      <c r="C81" s="11"/>
-      <c r="D81" s="12"/>
+      <c r="B81" s="9"/>
+      <c r="C81" s="9"/>
+      <c r="D81" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5771,658 +6209,658 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="5" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="9"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="7"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="9"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="7"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="9"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="7"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="9"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="7"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="9"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="7"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="9"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="7"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="9"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="7"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="9"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="7"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="9"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="7"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="9"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="7"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="9"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="7"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="9"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="7"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="9"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="7"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="9"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="7"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="9"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="7"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="9"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="7"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="9"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="7"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="9"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="7"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="9"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="7"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="9"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="7"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="9"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="7"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="9"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="7"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="9"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="7"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="9"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="7"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" s="8" t="s">
+      <c r="A26" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="9"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="7"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="9"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="7"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="9"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="7"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="9"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="7"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" s="8" t="s">
+      <c r="A30" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="9"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="7"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="9"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="7"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" s="8" t="s">
+      <c r="A32" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="9"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="7"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" s="8" t="s">
+      <c r="A33" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="9"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="7"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" s="8" t="s">
+      <c r="A34" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="9"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="7"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" s="8" t="s">
+      <c r="A35" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="9"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="7"/>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" s="8" t="s">
+      <c r="A36" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="9"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="7"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A37" s="8" t="s">
+      <c r="A37" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="9"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="7"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38" s="8" t="s">
+      <c r="A38" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="9"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="7"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39" s="8" t="s">
+      <c r="A39" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="9"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="7"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A40" s="8" t="s">
+      <c r="A40" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B40" s="4"/>
-      <c r="C40" s="4"/>
-      <c r="D40" s="9"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="7"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" s="8" t="s">
+      <c r="A41" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
-      <c r="D41" s="9"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="7"/>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42" s="8" t="s">
+      <c r="A42" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="9"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="7"/>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A43" s="8" t="s">
+      <c r="A43" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B43" s="4"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="9"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="7"/>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A44" s="8" t="s">
+      <c r="A44" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B44" s="4"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="9"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="7"/>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A45" s="8" t="s">
+      <c r="A45" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B45" s="4"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="9"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="7"/>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A46" s="8" t="s">
+      <c r="A46" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B46" s="4"/>
-      <c r="C46" s="4"/>
-      <c r="D46" s="9"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="7"/>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A47" s="8" t="s">
+      <c r="A47" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B47" s="4"/>
-      <c r="C47" s="4"/>
-      <c r="D47" s="9"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="7"/>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A48" s="8" t="s">
+      <c r="A48" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B48" s="4"/>
-      <c r="C48" s="4"/>
-      <c r="D48" s="9"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="7"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A49" s="8" t="s">
+      <c r="A49" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B49" s="4"/>
-      <c r="C49" s="4"/>
-      <c r="D49" s="9"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="7"/>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A50" s="8" t="s">
+      <c r="A50" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B50" s="4"/>
-      <c r="C50" s="4"/>
-      <c r="D50" s="9"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="7"/>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A51" s="8" t="s">
+      <c r="A51" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B51" s="4"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="9"/>
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="7"/>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A52" s="8" t="s">
+      <c r="A52" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B52" s="4"/>
-      <c r="C52" s="4"/>
-      <c r="D52" s="9"/>
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="7"/>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A53" s="8" t="s">
+      <c r="A53" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B53" s="4"/>
-      <c r="C53" s="4"/>
-      <c r="D53" s="9"/>
+      <c r="B53" s="2"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="7"/>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A54" s="8" t="s">
+      <c r="A54" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B54" s="4"/>
-      <c r="C54" s="4"/>
-      <c r="D54" s="9"/>
+      <c r="B54" s="2"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="7"/>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A55" s="8" t="s">
+      <c r="A55" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B55" s="4"/>
-      <c r="C55" s="4"/>
-      <c r="D55" s="9"/>
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="7"/>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A56" s="8" t="s">
+      <c r="A56" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="B56" s="4"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="9"/>
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="7"/>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A57" s="8" t="s">
+      <c r="A57" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="B57" s="4"/>
-      <c r="C57" s="4"/>
-      <c r="D57" s="9"/>
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="7"/>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A58" s="8" t="s">
+      <c r="A58" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="B58" s="4"/>
-      <c r="C58" s="4"/>
-      <c r="D58" s="9"/>
+      <c r="B58" s="2"/>
+      <c r="C58" s="2"/>
+      <c r="D58" s="7"/>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A59" s="8" t="s">
+      <c r="A59" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B59" s="4"/>
-      <c r="C59" s="4"/>
-      <c r="D59" s="9"/>
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="7"/>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A60" s="8" t="s">
+      <c r="A60" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B60" s="4"/>
-      <c r="C60" s="4"/>
-      <c r="D60" s="9"/>
+      <c r="B60" s="2"/>
+      <c r="C60" s="2"/>
+      <c r="D60" s="7"/>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A61" s="8" t="s">
+      <c r="A61" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="B61" s="4"/>
-      <c r="C61" s="4"/>
-      <c r="D61" s="9"/>
+      <c r="B61" s="2"/>
+      <c r="C61" s="2"/>
+      <c r="D61" s="7"/>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A62" s="8" t="s">
+      <c r="A62" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B62" s="4"/>
-      <c r="C62" s="4"/>
-      <c r="D62" s="9"/>
+      <c r="B62" s="2"/>
+      <c r="C62" s="2"/>
+      <c r="D62" s="7"/>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A63" s="8" t="s">
+      <c r="A63" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B63" s="4"/>
-      <c r="C63" s="4"/>
-      <c r="D63" s="9"/>
+      <c r="B63" s="2"/>
+      <c r="C63" s="2"/>
+      <c r="D63" s="7"/>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A64" s="8" t="s">
+      <c r="A64" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="B64" s="4"/>
-      <c r="C64" s="4"/>
-      <c r="D64" s="9"/>
+      <c r="B64" s="2"/>
+      <c r="C64" s="2"/>
+      <c r="D64" s="7"/>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A65" s="8" t="s">
+      <c r="A65" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B65" s="4"/>
-      <c r="C65" s="4"/>
-      <c r="D65" s="9"/>
+      <c r="B65" s="2"/>
+      <c r="C65" s="2"/>
+      <c r="D65" s="7"/>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A66" s="8" t="s">
+      <c r="A66" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="B66" s="4"/>
-      <c r="C66" s="4"/>
-      <c r="D66" s="9"/>
+      <c r="B66" s="2"/>
+      <c r="C66" s="2"/>
+      <c r="D66" s="7"/>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A67" s="8" t="s">
+      <c r="A67" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B67" s="4"/>
-      <c r="C67" s="4"/>
-      <c r="D67" s="9"/>
+      <c r="B67" s="2"/>
+      <c r="C67" s="2"/>
+      <c r="D67" s="7"/>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A68" s="8" t="s">
+      <c r="A68" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B68" s="4"/>
-      <c r="C68" s="4"/>
-      <c r="D68" s="9"/>
+      <c r="B68" s="2"/>
+      <c r="C68" s="2"/>
+      <c r="D68" s="7"/>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A69" s="8" t="s">
+      <c r="A69" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="B69" s="4"/>
-      <c r="C69" s="4"/>
-      <c r="D69" s="9"/>
+      <c r="B69" s="2"/>
+      <c r="C69" s="2"/>
+      <c r="D69" s="7"/>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A70" s="8" t="s">
+      <c r="A70" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B70" s="4"/>
-      <c r="C70" s="4"/>
-      <c r="D70" s="9"/>
+      <c r="B70" s="2"/>
+      <c r="C70" s="2"/>
+      <c r="D70" s="7"/>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A71" s="8" t="s">
+      <c r="A71" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B71" s="4"/>
-      <c r="C71" s="4"/>
-      <c r="D71" s="9"/>
+      <c r="B71" s="2"/>
+      <c r="C71" s="2"/>
+      <c r="D71" s="7"/>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A72" s="8" t="s">
+      <c r="A72" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="B72" s="4"/>
-      <c r="C72" s="4"/>
-      <c r="D72" s="9"/>
+      <c r="B72" s="2"/>
+      <c r="C72" s="2"/>
+      <c r="D72" s="7"/>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A73" s="8" t="s">
+      <c r="A73" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="B73" s="4"/>
-      <c r="C73" s="4"/>
-      <c r="D73" s="9"/>
+      <c r="B73" s="2"/>
+      <c r="C73" s="2"/>
+      <c r="D73" s="7"/>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A74" s="8" t="s">
+      <c r="A74" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="B74" s="4"/>
-      <c r="C74" s="4"/>
-      <c r="D74" s="9"/>
+      <c r="B74" s="2"/>
+      <c r="C74" s="2"/>
+      <c r="D74" s="7"/>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A75" s="8" t="s">
+      <c r="A75" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="B75" s="4"/>
-      <c r="C75" s="4"/>
-      <c r="D75" s="9"/>
+      <c r="B75" s="2"/>
+      <c r="C75" s="2"/>
+      <c r="D75" s="7"/>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A76" s="8" t="s">
+      <c r="A76" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="B76" s="4"/>
-      <c r="C76" s="4"/>
-      <c r="D76" s="9"/>
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="7"/>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A77" s="8" t="s">
+      <c r="A77" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="B77" s="4"/>
-      <c r="C77" s="4"/>
-      <c r="D77" s="9"/>
+      <c r="B77" s="2"/>
+      <c r="C77" s="2"/>
+      <c r="D77" s="7"/>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A78" s="8" t="s">
+      <c r="A78" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="B78" s="4"/>
-      <c r="C78" s="4"/>
-      <c r="D78" s="9"/>
+      <c r="B78" s="2"/>
+      <c r="C78" s="2"/>
+      <c r="D78" s="7"/>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A79" s="8" t="s">
+      <c r="A79" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="B79" s="4"/>
-      <c r="C79" s="4"/>
-      <c r="D79" s="9"/>
+      <c r="B79" s="2"/>
+      <c r="C79" s="2"/>
+      <c r="D79" s="7"/>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A80" s="8" t="s">
+      <c r="A80" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="B80" s="4"/>
-      <c r="C80" s="4"/>
-      <c r="D80" s="9"/>
+      <c r="B80" s="2"/>
+      <c r="C80" s="2"/>
+      <c r="D80" s="7"/>
     </row>
     <row r="81" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A81" s="10">
+      <c r="A81" s="8">
         <v>46753</v>
       </c>
-      <c r="B81" s="11"/>
-      <c r="C81" s="11"/>
-      <c r="D81" s="12"/>
+      <c r="B81" s="9"/>
+      <c r="C81" s="9"/>
+      <c r="D81" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6441,658 +6879,658 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="5" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="9"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="7"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="9"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="7"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="9"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="7"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="9"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="7"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="9"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="7"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="9"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="7"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="9"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="7"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="9"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="7"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="9"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="7"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="9"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="7"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="9"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="7"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="9"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="7"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="9"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="7"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="9"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="7"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="9"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="7"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="9"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="7"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="9"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="7"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="9"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="7"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="9"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="7"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="9"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="7"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="9"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="7"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="9"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="7"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="9"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="7"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="9"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="7"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" s="8" t="s">
+      <c r="A26" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="9"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="7"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="9"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="7"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="9"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="7"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="9"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="7"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" s="8" t="s">
+      <c r="A30" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="9"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="7"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="9"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="7"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" s="8" t="s">
+      <c r="A32" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="9"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="7"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" s="8" t="s">
+      <c r="A33" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="9"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="7"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" s="8" t="s">
+      <c r="A34" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="9"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="7"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" s="8" t="s">
+      <c r="A35" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="9"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="7"/>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" s="8" t="s">
+      <c r="A36" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="9"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="7"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A37" s="8" t="s">
+      <c r="A37" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="9"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="7"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38" s="8" t="s">
+      <c r="A38" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="9"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="7"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39" s="8" t="s">
+      <c r="A39" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="9"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="7"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A40" s="8" t="s">
+      <c r="A40" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B40" s="4"/>
-      <c r="C40" s="4"/>
-      <c r="D40" s="9"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="7"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" s="8" t="s">
+      <c r="A41" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
-      <c r="D41" s="9"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="7"/>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42" s="8" t="s">
+      <c r="A42" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="9"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="7"/>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A43" s="8" t="s">
+      <c r="A43" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B43" s="4"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="9"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="7"/>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A44" s="8" t="s">
+      <c r="A44" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B44" s="4"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="9"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="7"/>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A45" s="8" t="s">
+      <c r="A45" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B45" s="4"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="9"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="7"/>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A46" s="8" t="s">
+      <c r="A46" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B46" s="4"/>
-      <c r="C46" s="4"/>
-      <c r="D46" s="9"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="7"/>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A47" s="8" t="s">
+      <c r="A47" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B47" s="4"/>
-      <c r="C47" s="4"/>
-      <c r="D47" s="9"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="7"/>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A48" s="8" t="s">
+      <c r="A48" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B48" s="4"/>
-      <c r="C48" s="4"/>
-      <c r="D48" s="9"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="7"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A49" s="8" t="s">
+      <c r="A49" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B49" s="4"/>
-      <c r="C49" s="4"/>
-      <c r="D49" s="9"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="7"/>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A50" s="8" t="s">
+      <c r="A50" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B50" s="4"/>
-      <c r="C50" s="4"/>
-      <c r="D50" s="9"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="7"/>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A51" s="8" t="s">
+      <c r="A51" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B51" s="4"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="9"/>
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="7"/>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A52" s="8" t="s">
+      <c r="A52" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B52" s="4"/>
-      <c r="C52" s="4"/>
-      <c r="D52" s="9"/>
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="7"/>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A53" s="8" t="s">
+      <c r="A53" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B53" s="4"/>
-      <c r="C53" s="4"/>
-      <c r="D53" s="9"/>
+      <c r="B53" s="2"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="7"/>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A54" s="8" t="s">
+      <c r="A54" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B54" s="4"/>
-      <c r="C54" s="4"/>
-      <c r="D54" s="9"/>
+      <c r="B54" s="2"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="7"/>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A55" s="8" t="s">
+      <c r="A55" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B55" s="4"/>
-      <c r="C55" s="4"/>
-      <c r="D55" s="9"/>
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="7"/>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A56" s="8" t="s">
+      <c r="A56" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="B56" s="4"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="9"/>
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="7"/>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A57" s="8" t="s">
+      <c r="A57" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="B57" s="4"/>
-      <c r="C57" s="4"/>
-      <c r="D57" s="9"/>
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="7"/>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A58" s="8" t="s">
+      <c r="A58" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="B58" s="4"/>
-      <c r="C58" s="4"/>
-      <c r="D58" s="9"/>
+      <c r="B58" s="2"/>
+      <c r="C58" s="2"/>
+      <c r="D58" s="7"/>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A59" s="8" t="s">
+      <c r="A59" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B59" s="4"/>
-      <c r="C59" s="4"/>
-      <c r="D59" s="9"/>
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="7"/>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A60" s="8" t="s">
+      <c r="A60" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B60" s="4"/>
-      <c r="C60" s="4"/>
-      <c r="D60" s="9"/>
+      <c r="B60" s="2"/>
+      <c r="C60" s="2"/>
+      <c r="D60" s="7"/>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A61" s="8" t="s">
+      <c r="A61" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="B61" s="4"/>
-      <c r="C61" s="4"/>
-      <c r="D61" s="9"/>
+      <c r="B61" s="2"/>
+      <c r="C61" s="2"/>
+      <c r="D61" s="7"/>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A62" s="8" t="s">
+      <c r="A62" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B62" s="4"/>
-      <c r="C62" s="4"/>
-      <c r="D62" s="9"/>
+      <c r="B62" s="2"/>
+      <c r="C62" s="2"/>
+      <c r="D62" s="7"/>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A63" s="8" t="s">
+      <c r="A63" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B63" s="4"/>
-      <c r="C63" s="4"/>
-      <c r="D63" s="9"/>
+      <c r="B63" s="2"/>
+      <c r="C63" s="2"/>
+      <c r="D63" s="7"/>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A64" s="8" t="s">
+      <c r="A64" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="B64" s="4"/>
-      <c r="C64" s="4"/>
-      <c r="D64" s="9"/>
+      <c r="B64" s="2"/>
+      <c r="C64" s="2"/>
+      <c r="D64" s="7"/>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A65" s="8" t="s">
+      <c r="A65" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B65" s="4"/>
-      <c r="C65" s="4"/>
-      <c r="D65" s="9"/>
+      <c r="B65" s="2"/>
+      <c r="C65" s="2"/>
+      <c r="D65" s="7"/>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A66" s="8" t="s">
+      <c r="A66" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="B66" s="4"/>
-      <c r="C66" s="4"/>
-      <c r="D66" s="9"/>
+      <c r="B66" s="2"/>
+      <c r="C66" s="2"/>
+      <c r="D66" s="7"/>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A67" s="8" t="s">
+      <c r="A67" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B67" s="4"/>
-      <c r="C67" s="4"/>
-      <c r="D67" s="9"/>
+      <c r="B67" s="2"/>
+      <c r="C67" s="2"/>
+      <c r="D67" s="7"/>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A68" s="8" t="s">
+      <c r="A68" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B68" s="4"/>
-      <c r="C68" s="4"/>
-      <c r="D68" s="9"/>
+      <c r="B68" s="2"/>
+      <c r="C68" s="2"/>
+      <c r="D68" s="7"/>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A69" s="8" t="s">
+      <c r="A69" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="B69" s="4"/>
-      <c r="C69" s="4"/>
-      <c r="D69" s="9"/>
+      <c r="B69" s="2"/>
+      <c r="C69" s="2"/>
+      <c r="D69" s="7"/>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A70" s="8" t="s">
+      <c r="A70" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B70" s="4"/>
-      <c r="C70" s="4"/>
-      <c r="D70" s="9"/>
+      <c r="B70" s="2"/>
+      <c r="C70" s="2"/>
+      <c r="D70" s="7"/>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A71" s="8" t="s">
+      <c r="A71" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B71" s="4"/>
-      <c r="C71" s="4"/>
-      <c r="D71" s="9"/>
+      <c r="B71" s="2"/>
+      <c r="C71" s="2"/>
+      <c r="D71" s="7"/>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A72" s="8" t="s">
+      <c r="A72" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="B72" s="4"/>
-      <c r="C72" s="4"/>
-      <c r="D72" s="9"/>
+      <c r="B72" s="2"/>
+      <c r="C72" s="2"/>
+      <c r="D72" s="7"/>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A73" s="8" t="s">
+      <c r="A73" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="B73" s="4"/>
-      <c r="C73" s="4"/>
-      <c r="D73" s="9"/>
+      <c r="B73" s="2"/>
+      <c r="C73" s="2"/>
+      <c r="D73" s="7"/>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A74" s="8" t="s">
+      <c r="A74" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="B74" s="4"/>
-      <c r="C74" s="4"/>
-      <c r="D74" s="9"/>
+      <c r="B74" s="2"/>
+      <c r="C74" s="2"/>
+      <c r="D74" s="7"/>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A75" s="8" t="s">
+      <c r="A75" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="B75" s="4"/>
-      <c r="C75" s="4"/>
-      <c r="D75" s="9"/>
+      <c r="B75" s="2"/>
+      <c r="C75" s="2"/>
+      <c r="D75" s="7"/>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A76" s="8" t="s">
+      <c r="A76" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="B76" s="4"/>
-      <c r="C76" s="4"/>
-      <c r="D76" s="9"/>
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="7"/>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A77" s="8" t="s">
+      <c r="A77" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="B77" s="4"/>
-      <c r="C77" s="4"/>
-      <c r="D77" s="9"/>
+      <c r="B77" s="2"/>
+      <c r="C77" s="2"/>
+      <c r="D77" s="7"/>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A78" s="8" t="s">
+      <c r="A78" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="B78" s="4"/>
-      <c r="C78" s="4"/>
-      <c r="D78" s="9"/>
+      <c r="B78" s="2"/>
+      <c r="C78" s="2"/>
+      <c r="D78" s="7"/>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A79" s="8" t="s">
+      <c r="A79" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="B79" s="4"/>
-      <c r="C79" s="4"/>
-      <c r="D79" s="9"/>
+      <c r="B79" s="2"/>
+      <c r="C79" s="2"/>
+      <c r="D79" s="7"/>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A80" s="8" t="s">
+      <c r="A80" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="B80" s="4"/>
-      <c r="C80" s="4"/>
-      <c r="D80" s="9"/>
+      <c r="B80" s="2"/>
+      <c r="C80" s="2"/>
+      <c r="D80" s="7"/>
     </row>
     <row r="81" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A81" s="10">
+      <c r="A81" s="8">
         <v>46753</v>
       </c>
-      <c r="B81" s="11"/>
-      <c r="C81" s="11"/>
-      <c r="D81" s="12"/>
+      <c r="B81" s="9"/>
+      <c r="C81" s="9"/>
+      <c r="D81" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
